--- a/data.mn/public/datasets/meat-production-total.xlsx
+++ b/data.mn/public/datasets/meat-production-total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,7 +505,7 @@
         <v>2019</v>
       </c>
       <c r="B11" t="n">
-        <v>545029.2</v>
+        <v>543817.1</v>
       </c>
     </row>
     <row r="12">
@@ -513,7 +513,7 @@
         <v>2020</v>
       </c>
       <c r="B12" t="n">
-        <v>744516</v>
+        <v>746161.1</v>
       </c>
     </row>
     <row r="13">
@@ -521,7 +521,7 @@
         <v>2021</v>
       </c>
       <c r="B13" t="n">
-        <v>512679.2</v>
+        <v>506970.2</v>
       </c>
     </row>
     <row r="14">
@@ -529,7 +529,7 @@
         <v>2022</v>
       </c>
       <c r="B14" t="n">
-        <v>653966.6</v>
+        <v>650145.9</v>
       </c>
     </row>
     <row r="15">
@@ -537,7 +537,7 @@
         <v>2023</v>
       </c>
       <c r="B15" t="n">
-        <v>622082.7</v>
+        <v>668559.2</v>
       </c>
     </row>
     <row r="16">
@@ -545,7 +545,15 @@
         <v>2024</v>
       </c>
       <c r="B16" t="n">
-        <v>450443.1</v>
+        <v>453136.6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B17" t="n">
+        <v>699872.382</v>
       </c>
     </row>
   </sheetData>
